--- a/backend/MODULE_1_FINAL_RECONCILIATION.xlsx
+++ b/backend/MODULE_1_FINAL_RECONCILIATION.xlsx
@@ -46,9 +46,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="1">
     <font>

--- a/backend/MODULE_1_FINAL_RECONCILIATION.xlsx
+++ b/backend/MODULE_1_FINAL_RECONCILIATION.xlsx
@@ -46,8 +46,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1854,7 +1855,7 @@
         <v>2024-04-01</v>
       </c>
       <c r="H2" t="str">
-        <v>BASE_DOMESTIC_CURRENCY</v>
+        <v>Official Base Currency Parity</v>
       </c>
       <c r="I2" t="str">
         <v>FX_VALID</v>
